--- a/source-data/Enerium_Артефакты_Финал.xlsx
+++ b/source-data/Enerium_Артефакты_Финал.xlsx
@@ -14,8 +14,8 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Артефакты'!$A$1:$Q$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Уровни'!$A$1:$G$78</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Правила'!$A$1:$B$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Правки под систему'!$A$1:$D$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Правила'!$A$1:$B$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Правки под систему'!$A$1:$D$15</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -187,7 +187,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-01 — из данных игры сборщиком tools/content-gen/tables/build.py (содержимое — tools/content-gen/tables/collect.js)</t>
+          <t xml:space="preserve">2026-10-07 — из данных игры сборщиком tools/content-gen/tables/build.py (содержимое — tools/content-gen/tables/collect.js)</t>
         </is>
       </c>
     </row>
@@ -199,7 +199,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">7f0966d22ef3b359 — sha256 содержимого книги; по нему --check видит, что данные изменились</t>
+          <t xml:space="preserve">a6fd69a2ae85153c — sha256 содержимого книги; по нему --check видит, что данные изменились</t>
         </is>
       </c>
     </row>
@@ -260,7 +260,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">3 строки.</t>
+          <t xml:space="preserve">4 строки.</t>
         </is>
       </c>
     </row>
@@ -272,7 +272,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">13 строк.</t>
+          <t xml:space="preserve">14 строк.</t>
         </is>
       </c>
     </row>
@@ -302,8 +302,8 @@
 III — слабые, почти незаметные намёки — слово-отзвук без имени тайны (ADR-0022: намёки на Странника — с цикла III)
 IV — заметнее, но всё ещё намёки: иносказание, без прямых имён и формулировок тайны
 V — намёки очевиднее («начиная с 5 будут намёки»); прямого раскрытия §38 нет
-VI — только для команды: здесь тайны названы прямо
-Ступени слов: D — прямое раскрытие — только цикл VI, для команды; H3 — явный намёк — с цикла V; H2 — заметный намёк — с цикла IV; H1 — слабый намёк, слово-отзвук — с цикла III.
+VI — раскрытие: в текстах игрока цикла VI тайны могут быть названы прямо (ADR-0054); в текстах циклов I–V — нет
+Ступени слов: D — прямое раскрытие — только с цикла VI: игрок получает его в игре, раньше — нет; H3 — явный намёк — с цикла V; H2 — заметный намёк — с цикла IV; H1 — слабый намёк, слово-отзвук — с цикла III.
 Проверка — node tools/content-gen/tables/check_spoilers.js; все совпадения по циклам — «Реестр имён», лист «Намёки по циклам».</t>
         </is>
       </c>
@@ -461,14 +461,14 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Одновременных забегов</t>
+          <t xml:space="preserve">Активных биомов</t>
         </is>
       </c>
       <c r="G2">
         <v>1</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2">
         <v>5</v>
@@ -489,15 +489,19 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 → 6</t>
+          <t xml:space="preserve">0 → 6</t>
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Седьмой — пассивка Памяти «Право владыки»: до семи забегов разом (ADR-0014)</t>
-        </is>
-      </c>
-      <c r="Q2" s="3"/>
+          <t xml:space="preserve">Без «Знака» активного биома нет: покупка открывает первый, каждый уровень — ещё один. Седьмой — пассивка Памяти «Право владыки» (ADR-0014)</t>
+        </is>
+      </c>
+      <c r="Q2" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Слот забега даёт только этот артефакт (ADR-0054): покупка — в обучении, она открывает один активный биом, единственный в обучении; уровни I–V — с цикла II, по одному за цикл. Прежде первый слот был у всех с начала («1 → 6»), остальные приходили с номером цикла (ADR-0031, п. 3)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3">
@@ -1643,7 +1647,7 @@
         <v>600</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -1672,7 +1676,7 @@
         <v>1800</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -1701,7 +1705,7 @@
         <v>3600</v>
       </c>
       <c r="G4">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -1730,7 +1734,7 @@
         <v>6000</v>
       </c>
       <c r="G5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -1759,7 +1763,7 @@
         <v>9000</v>
       </c>
       <c r="G6">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -3943,7 +3947,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -3992,14 +3996,26 @@
         <v>7</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">trail</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B4"/>
+  <autoFilter ref="A1:B5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -4055,132 +4071,132 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Артефакт · № 2 «Ларец рядовых»</t>
+          <t xml:space="preserve">Артефакт · № 1 «Знак открытых троп»</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">+1 к верхней границе ресурсов с обычных врагов; уровней 6</t>
+          <t xml:space="preserve">+1 активный биом; уровней 5</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">+1 к верхней границе базовых ресурсов на этаже без элит; уровней 6; итог +6</t>
+          <t xml:space="preserve">+1 активный биом; уровней 5; итог 0 → 6</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Базовые ресурсы падают за этаж, а не с врага: за срабатывание — от одного до номера биома (ADR-0010, ADR-0023). «С обычных врагов» → «на этаже без элит»</t>
+          <t xml:space="preserve">Слот забега даёт только этот артефакт (ADR-0054): покупка — в обучении, она открывает один активный биом, единственный в обучении; уровни I–V — с цикла II, по одному за цикл. Прежде первый слот был у всех с начала («1 → 6»), остальные приходили с номером цикла (ADR-0031, п. 3)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Артефакт · № 3 «Ларец элит»</t>
+          <t xml:space="preserve">Артефакт · № 2 «Ларец рядовых»</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">+1 к верхней границе ресурсов с элит; уровней 6</t>
+          <t xml:space="preserve">+1 к верхней границе ресурсов с обычных врагов; уровней 6</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">+1 к верхней границе базовых ресурсов на этаже с элитой; уровней 6; итог +6</t>
+          <t xml:space="preserve">+1 к верхней границе базовых ресурсов на этаже без элит; уровней 6; итог +6</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">С элиты падают душа и ключ ремесла, базовые — за этаж (ADR-0010, ADR-0023). «С элит» → «на этаже с элитой»</t>
+          <t xml:space="preserve">Базовые ресурсы падают за этаж, а не с врага: за срабатывание — от одного до номера биома (ADR-0010, ADR-0023). «С обычных врагов» → «на этаже без элит»</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Артефакт · № 7 «Связка отмычек»</t>
+          <t xml:space="preserve">Артефакт · № 3 «Ларец элит»</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">+1 п.п. к шансу ключа с элит (1% → 7%); уровней 6</t>
+          <t xml:space="preserve">+1 к верхней границе ресурсов с элит; уровней 6</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">+1 п.п. к шансу рунного ключа с босса биома; уровней 6; итог +6 п.п.</t>
+          <t xml:space="preserve">+1 к верхней границе базовых ресурсов на этаже с элитой; уровней 6; итог +6</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Рунный ключ с элит не падает (ADR-0023, вариант Б) — отмычка поднимает шанс с босса биома</t>
+          <t xml:space="preserve">С элиты падают душа и ключ ремесла, базовые — за этаж (ADR-0010, ADR-0023). «С элит» → «на этаже с элитой»</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Артефакт · № 8 «Королевская отмычка»</t>
+          <t xml:space="preserve">Артефакт · № 7 «Связка отмычек»</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">+6 п.п. к шансу ключа с босса биома (1% → 25%); уровней 4</t>
+          <t xml:space="preserve">+1 п.п. к шансу ключа с элит (1% → 7%); уровней 6</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">+3 п.п. к шансу рунного ключа с босса биома; уровней 3; итог +9 п.п.</t>
+          <t xml:space="preserve">+1 п.п. к шансу рунного ключа с босса биома; уровней 6; итог +6 п.п.</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">База шанса с босса — 10 %, а не 1 % (recipes.js, §11: «10 % → 25 % с артефактами»). Вместе со «Связкой отмычек» (+6 п.п.) нужно ещё +9 п.п.: +3 п.п. за уровень, три уровня вместо четырёх</t>
+          <t xml:space="preserve">Рунный ключ с элит не падает (ADR-0023, вариант Б) — отмычка поднимает шанс с босса биома</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Артефакт · № 9 «Чутьё старьёвщика»</t>
+          <t xml:space="preserve">Артефакт · № 8 «Королевская отмычка»</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">+3 п.п. к шансу уникального ресурса босса (10% → 19%); уровней 3</t>
+          <t xml:space="preserve">+6 п.п. к шансу ключа с босса биома (1% → 25%); уровней 4</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">+3 п.п. к шансу уникального ресурса босса; уровней 3; итог +9 п.п.</t>
+          <t xml:space="preserve">+3 п.п. к шансу рунного ключа с босса биома; уровней 3; итог +9 п.п.</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Шанс уникального ресурса босса в данных — 5 % (recipes.js, §9.1), а не 10 %: «10 % → 19 %» → «5 % → 14 %»</t>
+          <t xml:space="preserve">База шанса с босса — 10 %, а не 1 % (recipes.js, §11: «10 % → 25 % с артефактами»). Вместе со «Связкой отмычек» (+6 п.п.) нужно ещё +9 п.п.: +3 п.п. за уровень, три уровня вместо четырёх</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Артефакт · № 12 «Доска у ворот»</t>
+          <t xml:space="preserve">Артефакт · № 9 «Чутьё старьёвщика»</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Доска объявлений</t>
+          <t xml:space="preserve">+3 п.п. к шансу уникального ресурса босса (10% → 19%); уровней 3</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Доска у ворот</t>
+          <t xml:space="preserve">+3 п.п. к шансу уникального ресурса босса; уровней 3; итог +9 п.п.</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">«Объявления» — слово нашего времени. У ворот Стоун-Хейма — доска заказов (свод); «Доска заказов» — уже прозвище героини Сельви (ADR-0038)</t>
+          <t xml:space="preserve">Шанс уникального ресурса босса в данных — 5 % (recipes.js, §9.1), а не 10 %: «10 % → 19 %» → «5 % → 14 %»</t>
         </is>
       </c>
     </row>
@@ -4192,131 +4208,153 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">+2 задание в пуле контрактов (1 → 9); уровней 4</t>
+          <t xml:space="preserve">Доска объявлений</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">+2 задания в пуле контрактов; уровней 4; итог 3 → 11</t>
+          <t xml:space="preserve">Доска у ворот</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Пул заданий по умолчанию — 3 (§18.2), а не 1: «1 → 9» → «3 → 11»</t>
+          <t xml:space="preserve">«Объявления» — слово нашего времени. У ворот Стоун-Хейма — доска заказов (свод); «Доска заказов» — уже прозвище героини Сельви (ADR-0038)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Артефакт · № 13 «Кости писаря»</t>
+          <t xml:space="preserve">Артефакт · № 12 «Доска у ворот»</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">+1 бесплатный реролл заданий (1 →3); уровней 2</t>
+          <t xml:space="preserve">+2 задание в пуле контрактов (1 → 9); уровней 4</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">+1 бесплатный реролл заданий; уровней 2; итог 3 → 5</t>
+          <t xml:space="preserve">+2 задания в пуле контрактов; уровней 4; итог 3 → 11</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Бесплатных рероллов по умолчанию — 3 (§18.2), а не 1: «1 → 3» → «3 → 5»</t>
+          <t xml:space="preserve">Пул заданий по умолчанию — 3 (§18.2), а не 1: «1 → 9» → «3 → 11»</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Артефакт · № 14 «Караванный шатёр»</t>
+          <t xml:space="preserve">Артефакт · № 13 «Кости писаря»</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">+2 слот ритуалов (1 →11); уровней 5</t>
+          <t xml:space="preserve">+1 бесплатный реролл заданий (1 →3); уровней 2</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">+2 слота ритуалов; уровней 3; итог 1 → 7</t>
+          <t xml:space="preserve">+1 бесплатный реролл заданий; уровней 2; итог 3 → 5</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Потолок слотов ритуалов — 7 (лист «Правила», п. 4), в §19.2 — «1 → ~8 артефактами»; строка давала 11. Три уровня вместо пяти: 1 → 7</t>
+          <t xml:space="preserve">Бесплатных рероллов по умолчанию — 3 (§18.2), а не 1: «1 → 3» → «3 → 5»</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Артефакт · № 18 «Опись прилавка»</t>
+          <t xml:space="preserve">Артефакт · № 14 «Караванный шатёр»</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Свиток ассортимента</t>
+          <t xml:space="preserve">+2 слот ритуалов (1 →11); уровней 5</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Опись прилавка</t>
+          <t xml:space="preserve">+2 слота ритуалов; уровней 3; итог 1 → 7</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">«Ассортимент» — слово нашего времени (ADR-0038)</t>
+          <t xml:space="preserve">Потолок слотов ритуалов — 7 (лист «Правила», п. 4), в §19.2 — «1 → ~8 артефактами»; строка давала 11. Три уровня вместо пяти: 1 → 7</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Артефакты · «Все уровни, души»</t>
+          <t xml:space="preserve">Артефакт · № 18 «Опись прилавка»</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">столбец таблицы</t>
+          <t xml:space="preserve">Свиток ассортимента</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">база × (1 + 2 + … + уровней)</t>
+          <t xml:space="preserve">Опись прилавка</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">По правилу автора «цена уровня = база × номер уровня» столбец считан по прежнему числу уровней — ещё у 7 артефактов, кроме правленых выше: Печать открытых троп: 3600 → 9000; Чутьё старьёвщика: 8000 → 4800; Зеркало призыва: 9000 → 2700; Доска объявлений: 4500 → 3000; Кости писаря: 2000 → 600; Вторая тропа: 4200 → 2100; Свиток ассортимента: 3150 → 2250</t>
+          <t xml:space="preserve">«Ассортимент» — слово нашего времени (ADR-0038)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t xml:space="preserve">Артефакты · «Все уровни, души»</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">столбец таблицы</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">база × (1 + 2 + … + уровней)</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">По правилу автора «цена уровня = база × номер уровня» столбец считан по прежнему числу уровней — ещё у 7 артефактов, кроме правленых выше: Печать открытых троп: 3600 → 9000; Чутьё старьёвщика: 8000 → 4800; Зеркало призыва: 9000 → 2700; Доска объявлений: 4500 → 3000; Кости писаря: 2000 → 600; Вторая тропа: 4200 → 2100; Свиток ассортимента: 3150 → 2250</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t xml:space="preserve">Артефакты · лист «Правила», п. 4</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">активных биомов максимум 4</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">до семи одновременных забегов: номер цикла и ещё один от Памяти</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ADR-0014, строка «Печати открытых троп» (+5, «всего 7 с учётом пассивки Странника»)</t>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">до семи одновременных забегов: шесть — «Знак открытых троп», ещё один — Память</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADR-0014, строка «Печати открытых троп» (+5, «всего 7 с учётом пассивки Странника»); слот даёт только артефакт — ADR-0054</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D14"/>
+  <autoFilter ref="A1:D15"/>
 </worksheet>
 </file>